--- a/research/traditional_assets/database/data/luxembourg/luxembourg_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_electronics_general.xlsx
@@ -587,26 +587,8 @@
           <t>Electronics (General)</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.194</v>
-      </c>
-      <c r="G2">
-        <v>0.1840607210626186</v>
-      </c>
-      <c r="H2">
-        <v>0.1595825426944971</v>
-      </c>
-      <c r="I2">
-        <v>0.08720141985546463</v>
-      </c>
-      <c r="J2">
-        <v>0.06984379125864228</v>
-      </c>
       <c r="K2">
-        <v>9.19</v>
-      </c>
-      <c r="L2">
-        <v>0.1743833017077799</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,70 +612,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>16.8</v>
+        <v>115.4</v>
       </c>
       <c r="V2">
-        <v>0.1546961325966851</v>
+        <v>1.03405017921147</v>
       </c>
       <c r="W2">
-        <v>0.1914583333333333</v>
+        <v>1.299319727891157</v>
       </c>
       <c r="X2">
-        <v>0.06760654808278931</v>
+        <v>0.1153124245446651</v>
       </c>
       <c r="Y2">
-        <v>0.123851785250544</v>
+        <v>1.184007303346492</v>
       </c>
       <c r="Z2">
-        <v>2.209882118578184</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0.1543465453961808</v>
+        <v>-0.01020553811019126</v>
       </c>
       <c r="AB2">
-        <v>0.06755889665737966</v>
+        <v>0.1153031288749933</v>
       </c>
       <c r="AC2">
-        <v>0.08678764873880118</v>
+        <v>-0.1255086669851846</v>
       </c>
       <c r="AD2">
-        <v>0.036</v>
+        <v>0.013</v>
       </c>
       <c r="AE2">
-        <v>0.06742586808506776</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.1034258680850678</v>
+        <v>0.013</v>
       </c>
       <c r="AG2">
-        <v>-16.69657413191493</v>
+        <v>-115.387</v>
       </c>
       <c r="AH2">
-        <v>0.000951449940598728</v>
+        <v>0.0001164738874503866</v>
       </c>
       <c r="AI2">
-        <v>0.001755854885532316</v>
+        <v>0.0001127366385403207</v>
       </c>
       <c r="AJ2">
-        <v>-0.1816752093211477</v>
+        <v>30.46923686295215</v>
       </c>
       <c r="AK2">
-        <v>-0.3965609398206037</v>
+        <v>1326.287356321789</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AM2">
-        <v>-3.22</v>
+        <v>3.74</v>
       </c>
       <c r="AN2">
-        <v>0.004580735462527039</v>
+        <v>0.01643489254108723</v>
+      </c>
+      <c r="AO2">
+        <v>-0.1147058823529412</v>
       </c>
       <c r="AP2">
-        <v>-2.124516367465954</v>
+        <v>-145.8748419721871</v>
       </c>
       <c r="AQ2">
-        <v>-1.409937888198758</v>
+        <v>-0.1147058823529412</v>
       </c>
     </row>
     <row r="3">
@@ -712,26 +697,8 @@
           <t>Electronics (General)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.194</v>
-      </c>
-      <c r="G3">
-        <v>0.1840607210626186</v>
-      </c>
-      <c r="H3">
-        <v>0.1595825426944971</v>
-      </c>
-      <c r="I3">
-        <v>0.08720141985546463</v>
-      </c>
-      <c r="J3">
-        <v>0.06984379125864228</v>
-      </c>
       <c r="K3">
-        <v>9.19</v>
-      </c>
-      <c r="L3">
-        <v>0.1743833017077799</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,70 +722,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>16.8</v>
+        <v>115.4</v>
       </c>
       <c r="V3">
-        <v>0.1546961325966851</v>
+        <v>1.03405017921147</v>
       </c>
       <c r="W3">
-        <v>0.1914583333333333</v>
+        <v>1.299319727891157</v>
       </c>
       <c r="X3">
-        <v>0.06760654808278931</v>
+        <v>0.1153124245446651</v>
       </c>
       <c r="Y3">
-        <v>0.123851785250544</v>
+        <v>1.184007303346492</v>
       </c>
       <c r="Z3">
-        <v>2.209882118578184</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.1543465453961808</v>
+        <v>-0.01020553811019126</v>
       </c>
       <c r="AB3">
-        <v>0.06755889665737966</v>
+        <v>0.1153031288749933</v>
       </c>
       <c r="AC3">
-        <v>0.08678764873880118</v>
+        <v>-0.1255086669851846</v>
       </c>
       <c r="AD3">
-        <v>0.036</v>
+        <v>0.013</v>
       </c>
       <c r="AE3">
-        <v>0.06742586808506776</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.1034258680850678</v>
+        <v>0.013</v>
       </c>
       <c r="AG3">
-        <v>-16.69657413191493</v>
+        <v>-115.387</v>
       </c>
       <c r="AH3">
-        <v>0.000951449940598728</v>
+        <v>0.0001164738874503866</v>
       </c>
       <c r="AI3">
-        <v>0.001755854885532316</v>
+        <v>0.0001127366385403207</v>
       </c>
       <c r="AJ3">
-        <v>-0.1816752093211477</v>
+        <v>30.46923686295215</v>
       </c>
       <c r="AK3">
-        <v>-0.3965609398206037</v>
+        <v>1326.287356321789</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AM3">
-        <v>-3.22</v>
+        <v>3.74</v>
       </c>
       <c r="AN3">
-        <v>0.004580735462527039</v>
+        <v>0.01643489254108723</v>
+      </c>
+      <c r="AO3">
+        <v>-0.1147058823529412</v>
       </c>
       <c r="AP3">
-        <v>-2.124516367465954</v>
+        <v>-145.8748419721871</v>
       </c>
       <c r="AQ3">
-        <v>-1.409937888198758</v>
+        <v>-0.1147058823529412</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_electronics_general.xlsx
@@ -587,8 +587,23 @@
           <t>Electronics (General)</t>
         </is>
       </c>
+      <c r="G2">
+        <v>-1.968388429752066</v>
+      </c>
+      <c r="H2">
+        <v>-2.055785123966942</v>
+      </c>
+      <c r="I2">
+        <v>-3.925619834710744</v>
+      </c>
+      <c r="J2">
+        <v>-3.925619834710744</v>
+      </c>
       <c r="K2">
-        <v>76.40000000000001</v>
+        <v>-20.3</v>
+      </c>
+      <c r="L2">
+        <v>-4.194214876033058</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -597,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -606,79 +621,64 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>115.4</v>
+        <v>42.4</v>
       </c>
       <c r="V2">
-        <v>1.03405017921147</v>
-      </c>
-      <c r="W2">
-        <v>1.299319727891157</v>
+        <v>0.2313147845062739</v>
       </c>
       <c r="X2">
-        <v>0.1153124245446651</v>
-      </c>
-      <c r="Y2">
-        <v>1.184007303346492</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>-0.01020553811019126</v>
+        <v>0.1086121498031633</v>
       </c>
       <c r="AB2">
-        <v>0.1153031288749933</v>
-      </c>
-      <c r="AC2">
-        <v>-0.1255086669851846</v>
+        <v>0.0948591099945939</v>
       </c>
       <c r="AD2">
-        <v>0.013</v>
+        <v>46.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.013</v>
+        <v>46.1</v>
       </c>
       <c r="AG2">
-        <v>-115.387</v>
+        <v>3.700000000000003</v>
       </c>
       <c r="AH2">
-        <v>0.0001164738874503866</v>
+        <v>0.2009590235396687</v>
       </c>
       <c r="AI2">
-        <v>0.0001127366385403207</v>
+        <v>0.3896872358410819</v>
       </c>
       <c r="AJ2">
-        <v>30.46923686295215</v>
+        <v>0.01978609625668451</v>
       </c>
       <c r="AK2">
-        <v>1326.287356321789</v>
+        <v>0.04874835309617922</v>
       </c>
       <c r="AL2">
-        <v>3.74</v>
+        <v>2.76</v>
       </c>
       <c r="AM2">
-        <v>3.74</v>
+        <v>1.969</v>
       </c>
       <c r="AN2">
-        <v>0.01643489254108723</v>
+        <v>-2.664739884393064</v>
       </c>
       <c r="AO2">
-        <v>-0.1147058823529412</v>
+        <v>-6.884057971014493</v>
       </c>
       <c r="AP2">
-        <v>-145.8748419721871</v>
+        <v>-0.2138728323699423</v>
       </c>
       <c r="AQ2">
-        <v>-0.1147058823529412</v>
+        <v>-9.649568308786186</v>
       </c>
     </row>
     <row r="3">
@@ -697,8 +697,23 @@
           <t>Electronics (General)</t>
         </is>
       </c>
+      <c r="G3">
+        <v>-1.968388429752066</v>
+      </c>
+      <c r="H3">
+        <v>-2.055785123966942</v>
+      </c>
+      <c r="I3">
+        <v>-3.925619834710744</v>
+      </c>
+      <c r="J3">
+        <v>-3.925619834710744</v>
+      </c>
       <c r="K3">
-        <v>76.40000000000001</v>
+        <v>-20.3</v>
+      </c>
+      <c r="L3">
+        <v>-4.194214876033058</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -707,7 +722,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -716,79 +731,64 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>115.4</v>
+        <v>42.4</v>
       </c>
       <c r="V3">
-        <v>1.03405017921147</v>
-      </c>
-      <c r="W3">
-        <v>1.299319727891157</v>
+        <v>0.2313147845062739</v>
       </c>
       <c r="X3">
-        <v>0.1153124245446651</v>
-      </c>
-      <c r="Y3">
-        <v>1.184007303346492</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>-0.01020553811019126</v>
+        <v>0.1086121498031633</v>
       </c>
       <c r="AB3">
-        <v>0.1153031288749933</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1255086669851846</v>
+        <v>0.0948591099945939</v>
       </c>
       <c r="AD3">
-        <v>0.013</v>
+        <v>46.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.013</v>
+        <v>46.1</v>
       </c>
       <c r="AG3">
-        <v>-115.387</v>
+        <v>3.700000000000003</v>
       </c>
       <c r="AH3">
-        <v>0.0001164738874503866</v>
+        <v>0.2009590235396687</v>
       </c>
       <c r="AI3">
-        <v>0.0001127366385403207</v>
+        <v>0.3896872358410819</v>
       </c>
       <c r="AJ3">
-        <v>30.46923686295215</v>
+        <v>0.01978609625668451</v>
       </c>
       <c r="AK3">
-        <v>1326.287356321789</v>
+        <v>0.04874835309617922</v>
       </c>
       <c r="AL3">
-        <v>3.74</v>
+        <v>2.76</v>
       </c>
       <c r="AM3">
-        <v>3.74</v>
+        <v>1.969</v>
       </c>
       <c r="AN3">
-        <v>0.01643489254108723</v>
+        <v>-2.664739884393064</v>
       </c>
       <c r="AO3">
-        <v>-0.1147058823529412</v>
+        <v>-6.884057971014493</v>
       </c>
       <c r="AP3">
-        <v>-145.8748419721871</v>
+        <v>-0.2138728323699423</v>
       </c>
       <c r="AQ3">
-        <v>-0.1147058823529412</v>
+        <v>-9.649568308786186</v>
       </c>
     </row>
   </sheetData>
